--- a/api/templates/module_swaps/uk.xlsx
+++ b/api/templates/module_swaps/uk.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25629"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26501"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\ahernandez\repos\aspect\api\templates\module_swaps\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-20.04\home\nsabaj\Repositories\aspect\api\templates\module_swaps\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E78231E-A2E4-413D-BA4A-A157B1A34906}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDB5C1B6-A40D-4813-8DE5-F2998D3B2CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Заміна модулів" sheetId="1" r:id="rId1"/>
@@ -223,7 +223,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -241,9 +241,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="3" applyFont="1"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -257,11 +254,27 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="1" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -663,171 +676,171 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I10"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="41.109375" customWidth="1"/>
-    <col min="2" max="2" width="24.21875" customWidth="1"/>
-    <col min="3" max="3" width="26.33203125" customWidth="1"/>
-    <col min="4" max="4" width="24.21875" customWidth="1"/>
-    <col min="5" max="5" width="15.88671875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="23.109375" customWidth="1"/>
-    <col min="7" max="7" width="15.88671875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="41.1328125" customWidth="1"/>
+    <col min="2" max="2" width="24.19921875" style="21" customWidth="1"/>
+    <col min="3" max="3" width="26.33203125" style="21" customWidth="1"/>
+    <col min="4" max="4" width="24.19921875" style="26" customWidth="1"/>
+    <col min="5" max="5" width="15.86328125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="23.1328125" customWidth="1"/>
+    <col min="7" max="7" width="15.86328125" style="1" customWidth="1"/>
     <col min="8" max="8" width="28" customWidth="1"/>
-    <col min="9" max="9" width="18.5546875" customWidth="1"/>
+    <col min="9" max="9" width="18.53125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="21" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:9" ht="21" x14ac:dyDescent="0.65">
       <c r="A1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="22"/>
       <c r="E1" s="3"/>
       <c r="F1" s="2"/>
       <c r="G1" s="3"/>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
     </row>
-    <row r="2" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="23"/>
       <c r="E2" s="6"/>
       <c r="F2" s="5"/>
       <c r="G2" s="6"/>
       <c r="H2" s="5"/>
       <c r="I2" s="5"/>
     </row>
-    <row r="3" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A3" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B3" s="5"/>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
+      <c r="B3" s="17"/>
+      <c r="C3" s="17"/>
+      <c r="D3" s="23"/>
       <c r="E3" s="6"/>
       <c r="F3" s="5"/>
       <c r="G3" s="6"/>
       <c r="H3" s="5"/>
       <c r="I3" s="5"/>
     </row>
-    <row r="4" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A4" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="5"/>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5"/>
+      <c r="B4" s="17"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="23"/>
       <c r="E4" s="6"/>
       <c r="F4" s="5"/>
       <c r="G4" s="6"/>
       <c r="H4" s="5"/>
       <c r="I4" s="5"/>
     </row>
-    <row r="5" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A5" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="5"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
+      <c r="B5" s="17"/>
+      <c r="C5" s="17"/>
+      <c r="D5" s="23"/>
       <c r="E5" s="6"/>
       <c r="F5" s="5"/>
       <c r="G5" s="6"/>
       <c r="H5" s="5"/>
       <c r="I5" s="5"/>
     </row>
-    <row r="6" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A6" s="4"/>
-      <c r="B6" s="5"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5"/>
+      <c r="B6" s="17"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="23"/>
       <c r="E6" s="6"/>
       <c r="F6" s="5"/>
       <c r="G6" s="6"/>
       <c r="H6" s="5"/>
       <c r="I6" s="5"/>
     </row>
-    <row r="7" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A7" s="8" t="str">
         <f>"Відсоток заміни модулів в рамках SLA: "&amp;TEXT(COUNTIF(D10:D10002,"&lt;=8")/COUNTIF(D10:D10002,"&lt;&gt;"),"0%")</f>
         <v>Відсоток заміни модулів в рамках SLA: 0%</v>
       </c>
-      <c r="B7" s="9"/>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
+      <c r="B7" s="18"/>
+      <c r="C7" s="17"/>
+      <c r="D7" s="23"/>
       <c r="E7" s="6"/>
       <c r="F7" s="5"/>
       <c r="G7" s="6"/>
       <c r="H7" s="5"/>
       <c r="I7" s="5"/>
     </row>
-    <row r="8" spans="1:9" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="10" t="s">
+    <row r="8" spans="1:9" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="5"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
+      <c r="B8" s="17"/>
+      <c r="C8" s="17"/>
+      <c r="D8" s="23"/>
       <c r="E8" s="6"/>
       <c r="F8" s="5"/>
       <c r="G8" s="6"/>
       <c r="H8" s="5"/>
       <c r="I8" s="5"/>
     </row>
-    <row r="9" spans="1:9" ht="31.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="11" t="s">
+    <row r="9" spans="1:9" ht="31.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A9" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="12" t="s">
+      <c r="B9" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="12" t="s">
+      <c r="C9" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="12" t="s">
+      <c r="D9" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="E9" s="12" t="s">
+      <c r="E9" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="F9" s="12" t="s">
+      <c r="F9" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="G9" s="12" t="s">
+      <c r="G9" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="H9" s="13" t="s">
+      <c r="H9" s="12" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="14" t="s">
+    <row r="10" spans="1:9" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A10" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="B10" s="14" t="s">
+      <c r="B10" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="C10" s="14" t="s">
+      <c r="C10" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="D10" s="15" t="s">
+      <c r="D10" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="E10" s="14" t="s">
+      <c r="E10" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="F10" s="16" t="s">
+      <c r="F10" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="G10" s="14" t="s">
+      <c r="G10" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="H10" s="17" t="s">
+      <c r="H10" s="15" t="s">
         <v>8</v>
       </c>
     </row>

--- a/api/templates/module_swaps/uk.xlsx
+++ b/api/templates/module_swaps/uk.xlsx
@@ -1,46 +1,66 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26501"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-20.04\home\nsabaj\Repositories\aspect\api\templates\module_swaps\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDB5C1B6-A40D-4813-8DE5-F2998D3B2CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875"/>
   </bookViews>
   <sheets>
-    <sheet name="Заміна модулів" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="Заміна модулів" state="visible" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+  <si>
+    <t>Заміна модулів</t>
+  </si>
+  <si>
+    <t>Дати: &lt;Dates&gt;</t>
+  </si>
+  <si>
+    <t>Області: &lt;States&gt;</t>
+  </si>
+  <si>
+    <t>Райони: &lt;Lgas&gt;</t>
+  </si>
+  <si>
+    <t>Сайти: &lt;Sites&gt;</t>
+  </si>
+  <si>
+    <t>&lt;DecommissionedDevicesLabel&gt;: &lt;DecommissionedDevices&gt;</t>
+  </si>
   <si>
     <t>&lt;Table&gt;</t>
   </si>
   <si>
+    <t>Ім'я пристрою</t>
+  </si>
+  <si>
+    <t>Дата останнього результату на старому модулі</t>
+  </si>
+  <si>
+    <t>Дата першого результату нового модуля</t>
+  </si>
+  <si>
+    <t>Кількість днів між цими датами</t>
+  </si>
+  <si>
+    <t>Серіальний інструмент</t>
+  </si>
+  <si>
+    <t>Старий модуль серіал</t>
+  </si>
+  <si>
+    <t>Новий модуль серіал</t>
+  </si>
+  <si>
+    <t>Модуль</t>
+  </si>
+  <si>
     <t>&lt;deviceName&gt;</t>
   </si>
   <si>
@@ -63,105 +83,66 @@
   </si>
   <si>
     <t>&lt;moduleName&gt;</t>
-  </si>
-  <si>
-    <t>Заміна модулів</t>
-  </si>
-  <si>
-    <t>Дати: &lt;Dates&gt;</t>
-  </si>
-  <si>
-    <t>Райони: &lt;Lgas&gt;</t>
-  </si>
-  <si>
-    <t>Сайти: &lt;Sites&gt;</t>
-  </si>
-  <si>
-    <t>Ім'я пристрою</t>
-  </si>
-  <si>
-    <t>Дата останнього результату на старому модулі</t>
-  </si>
-  <si>
-    <t>Дата першого результату нового модуля</t>
-  </si>
-  <si>
-    <t>Кількість днів між цими датами</t>
-  </si>
-  <si>
-    <t>Серіальний інструмент</t>
-  </si>
-  <si>
-    <t>Старий модуль серіал</t>
-  </si>
-  <si>
-    <t>Новий модуль серіал</t>
-  </si>
-  <si>
-    <t>Модуль</t>
-  </si>
-  <si>
-    <t>Області: &lt;States&gt;</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="dd\-mm\-yyyy;@"/>
+    <numFmt numFmtId="164" formatCode="dd-mm-yyyy;@"/>
   </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
+      <color theme="1"/>
+      <family val="2"/>
+      <scheme val="minor"/>
       <sz val="11"/>
-      <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
-      <sz val="12"/>
+      <charset val="1"/>
       <color rgb="FF000000"/>
+      <family val="2"/>
+      <sz val="11"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <b/>
+      <charset val="1"/>
+      <color rgb="FF000000"/>
+      <family val="2"/>
       <sz val="16"/>
-      <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <b/>
+      <charset val="204"/>
+      <color rgb="FF000000"/>
+      <family val="2"/>
       <sz val="16"/>
-      <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="204"/>
     </font>
     <font>
+      <charset val="204"/>
+      <color rgb="FF000000"/>
+      <family val="2"/>
       <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <charset val="1"/>
       <color rgb="FF000000"/>
+      <family val="2"/>
+      <sz val="12"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="204"/>
     </font>
     <font>
       <b/>
+      <charset val="1"/>
+      <family val="2"/>
       <sz val="12"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -187,102 +168,86 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="medium"/>
+      <bottom style="medium"/>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="4">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="3" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="1" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="4">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
-    <cellStyle name="Normal 3" xfId="3" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
-    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFBF30B"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -290,83 +255,8 @@
         </patternFill>
       </fill>
     </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFBF30B"/>
-        </patternFill>
-      </fill>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="FF000000"/>
-      <rgbColor rgb="FFFFFFFF"/>
-      <rgbColor rgb="FFFF0000"/>
-      <rgbColor rgb="FF00FF00"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FFFBF30B"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008000"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FF808000"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFC0C0C0"/>
-      <rgbColor rgb="FF808080"/>
-      <rgbColor rgb="FF9999FF"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFFFFCC"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FF660066"/>
-      <rgbColor rgb="FFFF8080"/>
-      <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFCCCCFF"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFCCFFCC"/>
-      <rgbColor rgb="FFFFFF99"/>
-      <rgbColor rgb="FF99CCFF"/>
-      <rgbColor rgb="FFFF99CC"/>
-      <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFFCC99"/>
-      <rgbColor rgb="FF3366FF"/>
-      <rgbColor rgb="FF3CC0DD"/>
-      <rgbColor rgb="FF99CC00"/>
-      <rgbColor rgb="FFFFCC00"/>
-      <rgbColor rgb="FFFF9900"/>
-      <rgbColor rgb="FFFF6600"/>
-      <rgbColor rgb="FF666699"/>
-      <rgbColor rgb="FF969696"/>
-      <rgbColor rgb="FF003366"/>
-      <rgbColor rgb="FF339966"/>
-      <rgbColor rgb="FF003300"/>
-      <rgbColor rgb="FF333300"/>
-      <rgbColor rgb="FF993300"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FF333399"/>
-      <rgbColor rgb="FF333333"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -674,188 +564,190 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I10"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.25" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.45" defaultColWidth="8.6640625" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="41.1328125" customWidth="1"/>
-    <col min="2" max="2" width="24.19921875" style="21" customWidth="1"/>
-    <col min="3" max="3" width="26.33203125" style="21" customWidth="1"/>
-    <col min="4" max="4" width="24.19921875" style="26" customWidth="1"/>
-    <col min="5" max="5" width="15.86328125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="24.19921875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="26.33203125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="24.19921875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="15.86328125" style="3" customWidth="1"/>
     <col min="6" max="6" width="23.1328125" customWidth="1"/>
-    <col min="7" max="7" width="15.86328125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="15.86328125" style="3" customWidth="1"/>
     <col min="8" max="8" width="28" customWidth="1"/>
     <col min="9" max="9" width="18.53125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="21" x14ac:dyDescent="0.65">
-      <c r="A1" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-    </row>
-    <row r="2" spans="1:9" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="A2" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="23"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
-    </row>
-    <row r="3" spans="1:9" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="A3" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B3" s="17"/>
-      <c r="C3" s="17"/>
-      <c r="D3" s="23"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="6"/>
-      <c r="H3" s="5"/>
-      <c r="I3" s="5"/>
-    </row>
-    <row r="4" spans="1:9" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="A4" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="23"/>
-      <c r="E4" s="6"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="6"/>
-      <c r="H4" s="5"/>
-      <c r="I4" s="5"/>
-    </row>
-    <row r="5" spans="1:9" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="A5" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="17"/>
-      <c r="C5" s="17"/>
-      <c r="D5" s="23"/>
-      <c r="E5" s="6"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="6"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5"/>
-    </row>
-    <row r="6" spans="1:9" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="A6" s="4"/>
-      <c r="B6" s="17"/>
-      <c r="C6" s="17"/>
-      <c r="D6" s="23"/>
-      <c r="E6" s="6"/>
-      <c r="F6" s="5"/>
-      <c r="G6" s="6"/>
-      <c r="H6" s="5"/>
-      <c r="I6" s="5"/>
-    </row>
-    <row r="7" spans="1:9" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="1" ht="21" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+    </row>
+    <row r="2" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="9"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="11"/>
+      <c r="F2" s="12"/>
+      <c r="G2" s="11"/>
+      <c r="H2" s="12"/>
+      <c r="I2" s="12"/>
+    </row>
+    <row r="3" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="9"/>
+      <c r="C3" s="9"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="11"/>
+      <c r="F3" s="12"/>
+      <c r="G3" s="11"/>
+      <c r="H3" s="12"/>
+      <c r="I3" s="12"/>
+    </row>
+    <row r="4" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="9"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="11"/>
+      <c r="F4" s="12"/>
+      <c r="G4" s="11"/>
+      <c r="H4" s="12"/>
+      <c r="I4" s="12"/>
+    </row>
+    <row r="5" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="9"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="10"/>
+      <c r="E5" s="11"/>
+      <c r="F5" s="12"/>
+      <c r="G5" s="11"/>
+      <c r="H5" s="12"/>
+      <c r="I5" s="12"/>
+    </row>
+    <row r="6" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="9"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="10"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="12"/>
+      <c r="I6" s="12"/>
+    </row>
+    <row r="7" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="str">
         <f>"Відсоток заміни модулів в рамках SLA: "&amp;TEXT(COUNTIF(D10:D10002,"&lt;=8")/COUNTIF(D10:D10002,"&lt;&gt;"),"0%")</f>
         <v>Відсоток заміни модулів в рамках SLA: 0%</v>
       </c>
-      <c r="B7" s="18"/>
-      <c r="C7" s="17"/>
-      <c r="D7" s="23"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="5"/>
-      <c r="G7" s="6"/>
-      <c r="H7" s="5"/>
-      <c r="I7" s="5"/>
-    </row>
-    <row r="8" spans="1:9" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="B8" s="17"/>
-      <c r="C8" s="17"/>
-      <c r="D8" s="23"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="5"/>
-      <c r="I8" s="5"/>
-    </row>
-    <row r="9" spans="1:9" ht="31.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A9" s="10" t="s">
+      <c r="B7" s="14"/>
+      <c r="C7" s="9"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="11"/>
+      <c r="F7" s="12"/>
+      <c r="G7" s="11"/>
+      <c r="H7" s="12"/>
+      <c r="I7" s="12"/>
+    </row>
+    <row r="8" ht="16.15" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="9"/>
+      <c r="C8" s="9"/>
+      <c r="D8" s="10"/>
+      <c r="E8" s="11"/>
+      <c r="F8" s="12"/>
+      <c r="G8" s="11"/>
+      <c r="H8" s="12"/>
+      <c r="I8" s="12"/>
+    </row>
+    <row r="9" ht="31.05" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="F9" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="19" t="s">
+      <c r="H9" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="19" t="s">
+    </row>
+    <row r="10" ht="15.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="24" t="s">
+      <c r="B10" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="E9" s="11" t="s">
+      <c r="C10" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="F9" s="11" t="s">
+      <c r="D10" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="G9" s="11" t="s">
+      <c r="E10" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="H9" s="12" t="s">
+      <c r="F10" s="24" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="A10" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="B10" s="20" t="s">
-        <v>2</v>
-      </c>
-      <c r="C10" s="20" t="s">
-        <v>3</v>
-      </c>
-      <c r="D10" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="E10" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="F10" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="G10" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="H10" s="15" t="s">
-        <v>8</v>
+      <c r="G10" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="H10" s="25" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="D8 D10:D1000001">
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="greaterThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D10">
-    <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
       <formula>""</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/api/templates/module_swaps/uk.xlsx
+++ b/api/templates/module_swaps/uk.xlsx
@@ -205,9 +205,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="14" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>

--- a/api/templates/module_swaps/uk.xlsx
+++ b/api/templates/module_swaps/uk.xlsx
@@ -31,7 +31,7 @@
     <t>Сайти: &lt;Sites&gt;</t>
   </si>
   <si>
-    <t>&lt;DecommissionedDevicesLabel&gt;: &lt;DecommissionedDevices&gt;</t>
+    <t>Виведені з експлуатації пристрої: &lt;DecommissionedDevices&gt;</t>
   </si>
   <si>
     <t>&lt;Table&gt;</t>
@@ -205,7 +205,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
